--- a/输出样本/测试结果_deepseek_v4.xlsx
+++ b/输出样本/测试结果_deepseek_v4.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. 260007 1.578 5000 05.21+0 潮州农商银行 请求 出给 平安证券2k + 平安银行3k</t>
+          <t>1. 210210 1.565 6000 +0 太原农商银行 6k 出给 乾县农联社 3k请求+旬邑农联社 2k请求+礼泉农联社 1k请求</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,33 +504,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>潮州农商银行</t>
+          <t>太原农商银行</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>260007</v>
+        <v>210210</v>
       </c>
       <c r="G2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.578</v>
+        <v>1.565</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>上家潮州农商银行，下家平安证券、平安银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家太原农商银行，下家乾县农联社、旬邑农联社、礼泉农联社，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 260007 1.578 5000 05.21+0 潮州农商银行 请求 出给 平安证券2k + 平安银行3k</t>
+          <t>1. 210210 1.565 6000 +0 太原农商银行 6k 出给 乾县农联社 3k请求+旬邑农联社 2k请求+礼泉农联社 1k请求</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,33 +545,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>平安证券</t>
+          <t>乾县农联社</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>260007</v>
+        <v>210210</v>
       </c>
       <c r="G3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.578</v>
+        <v>1.565</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>上家潮州农商银行，下家平安证券、平安银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家太原农商银行，下家乾县农联社、旬邑农联社、礼泉农联社，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. 260007 1.578 5000 05.21+0 潮州农商银行 请求 出给 平安证券2k + 平安银行3k</t>
+          <t>1. 210210 1.565 6000 +0 太原农商银行 6k 出给 乾县农联社 3k请求+旬邑农联社 2k请求+礼泉农联社 1k请求</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,38 +586,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>平安银行</t>
+          <t>旬邑农联社</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>260007</v>
+        <v>210210</v>
       </c>
       <c r="G4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.578</v>
+        <v>1.565</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>上家潮州农商银行，下家平安证券、平安银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家太原农商银行，下家乾县农联社、旬邑农联社、礼泉农联社，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. 250210 1.81 5000 05.21+0 启东农商银行 出给 陕西陇县农商行 请求</t>
+          <t>1. 210210 1.565 6000 +0 太原农商银行 6k 出给 乾县农联社 3k请求+旬邑农联社 2k请求+礼泉农联社 1k请求</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -627,38 +627,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>启东农商银行</t>
+          <t>礼泉农联社</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>250210</v>
+        <v>210210</v>
       </c>
       <c r="G5" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.565</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>上家启东农商银行，下家陕西陇县农商行，履行做市商职责，上下家不偏离。</t>
+          <t>上家太原农商银行，下家乾县农联社、旬邑农联社、礼泉农联社，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2. 250210 1.81 5000 05.21+0 启东农商银行 出给 陕西陇县农商行 请求</t>
+          <t>2. 240205 1.7075 3000 +0 陕西岐山农商银行 3k请求 + 太原农商银行 2k + 渭南市临渭农联社 1k 出给 陕西杨凌农商行 6k请求</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -668,33 +668,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>陕西陇县农商行</t>
+          <t>陕西岐山农商银行</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>250210</v>
+        <v>240205</v>
       </c>
       <c r="G6" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81</v>
+        <v>1.7075</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>上家启东农商银行，下家陕西陇县农商行，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西岐山农商银行、太原农商银行、渭南市临渭农联社，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3. 250215 1.815 1000 05.21+0 启东农商银行 出给 山东滕州农商行 请求</t>
+          <t>2. 240205 1.7075 3000 +0 陕西岐山农商银行 3k请求 + 太原农商银行 2k + 渭南市临渭农联社 1k 出给 陕西杨凌农商行 6k请求</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,38 +709,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>启东农商银行</t>
+          <t>太原农商银行</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>250215</v>
+        <v>240205</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.815</v>
+        <v>1.7075</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>上家启东农商银行，下家山东滕州农商行，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西岐山农商银行、太原农商银行、渭南市临渭农联社，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3. 250215 1.815 1000 05.21+0 启东农商银行 出给 山东滕州农商行 请求</t>
+          <t>2. 240205 1.7075 3000 +0 陕西岐山农商银行 3k请求 + 太原农商银行 2k + 渭南市临渭农联社 1k 出给 陕西杨凌农商行 6k请求</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -750,38 +750,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>山东滕州农商行</t>
+          <t>渭南市临渭农联社</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>250215</v>
+        <v>240205</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.815</v>
+        <v>1.7075</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>上家启东农商银行，下家山东滕州农商行，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西岐山农商银行、太原农商银行、渭南市临渭农联社，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1) 29.66Y 260002 2.265 4000 05.21+0 内蒙古农商银行4K 出给 平安银行3K+ 平安证券1K</t>
+          <t>2. 240205 1.7075 3000 +0 陕西岐山农商银行 3k请求 + 太原农商银行 2k + 渭南市临渭农联社 1k 出给 陕西杨凌农商行 6k请求</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -791,38 +791,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>内蒙古农商银行</t>
+          <t>陕西杨凌农商行</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>260002</v>
+        <v>240205</v>
       </c>
       <c r="G9" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.265</v>
+        <v>1.7075</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>上家内蒙古农商银行，下家平安银行、平安证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西岐山农商银行、太原农商银行、渭南市临渭农联社，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1) 29.66Y 260002 2.265 4000 05.21+0 内蒙古农商银行4K 出给 平安银行3K+ 平安证券1K</t>
+          <t>3. 240215 1.735 2000 +0 德州陵城农商银行 请求 出给 浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -832,33 +832,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>平安银行</t>
+          <t>德州陵城农商银行</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>260002</v>
+        <v>240215</v>
       </c>
       <c r="G10" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.265</v>
+        <v>1.735</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>上家内蒙古农商银行，下家平安银行、平安证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家德州陵城农商银行，下家浙江绍兴恒信农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1) 29.66Y 260002 2.265 4000 05.21+0 内蒙古农商银行4K 出给 平安银行3K+ 平安证券1K</t>
+          <t>3. 240215 1.735 2000 +0 德州陵城农商银行 请求 出给 浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -873,33 +873,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>平安证券</t>
+          <t>浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>260002</v>
+        <v>240215</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H11" t="n">
-        <v>2.265</v>
+        <v>1.735</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>上家内蒙古农商银行，下家平安银行、平安证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家德州陵城农商银行，下家浙江绍兴恒信农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2) 29.93Y 2600002 2.2325 3000 05.21+0 平安银行2K+ 浙江绍兴瑞丰农商银行1K 出给 杭州银行资管3K</t>
+          <t>4. 250022 1.739 1000 +0 东海农商银行 出给 山西孝义农商银行 请求</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -914,38 +914,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>平安银行</t>
+          <t>东海农商银行</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2600002</v>
+        <v>250022</v>
       </c>
       <c r="G12" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2325</v>
+        <v>1.739</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>上家平安银行、浙江绍兴瑞丰农商银行，下家杭州银行资管，履行做市商职责，上下家不偏离。</t>
+          <t>上家东海农商银行，下家山西孝义农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2) 29.93Y 2600002 2.2325 3000 05.21+0 平安银行2K+ 浙江绍兴瑞丰农商银行1K 出给 杭州银行资管3K</t>
+          <t>4. 250022 1.739 1000 +0 东海农商银行 出给 山西孝义农商银行 请求</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -955,38 +955,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>浙江绍兴瑞丰农商银行</t>
+          <t>山西孝义农商银行</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2600002</v>
+        <v>250022</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2325</v>
+        <v>1.739</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>上家平安银行、浙江绍兴瑞丰农商银行，下家杭州银行资管，履行做市商职责，上下家不偏离。</t>
+          <t>上家东海农商银行，下家山西孝义农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2) 29.93Y 2600002 2.2325 3000 05.21+0 平安银行2K+ 浙江绍兴瑞丰农商银行1K 出给 杭州银行资管3K</t>
+          <t>5. 240215 1.745 1000 +0 酒泉农商行 请求 出给 浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -996,38 +996,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>杭州银行资管</t>
+          <t>酒泉农商行</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2600002</v>
+        <v>240215</v>
       </c>
       <c r="G14" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2325</v>
+        <v>1.745</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>上家平安银行、浙江绍兴瑞丰农商银行，下家杭州银行资管，履行做市商职责，上下家不偏离。</t>
+          <t>上家酒泉农商行，下家浙江绍兴恒信农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3) 29.65Y 260002 2.268 1E +0 内蒙古农商银行 出给 华福证券</t>
+          <t>5. 240215 1.745 1000 +0 酒泉农商行 请求 出给 浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1037,38 +1037,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>内蒙古农商银行</t>
+          <t>浙江绍兴恒信农商银行</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>260002</v>
+        <v>240215</v>
       </c>
       <c r="G15" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.268</v>
+        <v>1.745</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>上家内蒙古农商银行，下家华福证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家酒泉农商行，下家浙江绍兴恒信农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3) 29.65Y 260002 2.268 1E +0 内蒙古农商银行 出给 华福证券</t>
+          <t>6. 230009 2.2625 5000 +0 东方证券 2k+ 华源证券 3k 出给 东营莱商村镇银行 5k请求</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1078,33 +1078,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>华福证券</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>260002</v>
+        <v>230009</v>
       </c>
       <c r="G16" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.268</v>
+        <v>2.2625</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>上家内蒙古农商银行，下家华福证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家东方证券、华源证券，下家东营莱商村镇银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4) 9.08Y 250215 1.813 5000 05.21+0 宁波通商银行 出给 陕西太白农商银行</t>
+          <t>6. 230009 2.2625 5000 +0 东方证券 2k+ 华源证券 3k 出给 东营莱商村镇银行 5k请求</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1119,33 +1119,33 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宁波通商银行</t>
+          <t>华源证券</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>250215</v>
+        <v>230009</v>
       </c>
       <c r="G17" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.813</v>
+        <v>2.2625</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>上家宁波通商银行，下家陕西太白农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家东方证券、华源证券，下家东营莱商村镇银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4) 9.08Y 250215 1.813 5000 05.21+0 宁波通商银行 出给 陕西太白农商银行</t>
+          <t>6. 230009 2.2625 5000 +0 东方证券 2k+ 华源证券 3k 出给 东营莱商村镇银行 5k请求</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1160,33 +1160,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>陕西太白农商银行</t>
+          <t>东营莱商村镇银行</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>250215</v>
+        <v>230009</v>
       </c>
       <c r="G18" t="n">
         <v>5000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.813</v>
+        <v>2.2625</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>上家宁波通商银行，下家陕西太白农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家东方证券、华源证券，下家东营莱商村镇银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1） 250014 1.365 5000 +0 苍南农商行 出给 辽沈银行</t>
+          <t>1. 260205 1.784 4000 +0 盘县农联社 1K 请求 +武功县农信社 3K 请求 出给 上海攀赢基金公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1201,38 +1201,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>苍南农商行</t>
+          <t>盘县农联社</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>250014</v>
+        <v>260205</v>
       </c>
       <c r="G19" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.365</v>
+        <v>1.784</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>上家苍南农商行，下家辽沈银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家盘县农联社、武功县农信社，下家上海攀赢基金公司，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1） 250014 1.365 5000 +0 苍南农商行 出给 辽沈银行</t>
+          <t>1. 260205 1.784 4000 +0 盘县农联社 1K 请求 +武功县农信社 3K 请求 出给 上海攀赢基金公司</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1242,38 +1242,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>辽沈银行</t>
+          <t>武功县农信社</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>250014</v>
+        <v>260205</v>
       </c>
       <c r="G20" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.365</v>
+        <v>1.784</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>上家苍南农商行，下家辽沈银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家盘县农联社、武功县农信社，下家上海攀赢基金公司，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1、 210220 2.069 2000 +0 湖北兴山农商银行 出给 沧州银行</t>
+          <t>1. 260205 1.784 4000 +0 盘县农联社 1K 请求 +武功县农信社 3K 请求 出给 上海攀赢基金公司</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1283,38 +1283,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>湖北兴山农商银行</t>
+          <t>上海攀赢基金公司</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>210220</v>
+        <v>260205</v>
       </c>
       <c r="G21" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H21" t="n">
-        <v>2.069</v>
+        <v>1.784</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>上家湖北兴山农商银行，下家沧州银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家盘县农联社、武功县农信社，下家上海攀赢基金公司，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1、 210220 2.069 2000 +0 湖北兴山农商银行 出给 沧州银行</t>
+          <t>2. 250205 1.77 1E +0 赣州农商行 4K 请求 +陕西陇县农商行6K 请求 出给 汇添富基金5K 请求 + 潍坊银行 2K + 平安银行3K</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1324,33 +1324,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>沧州银行</t>
+          <t>赣州农商行</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>210220</v>
+        <v>250205</v>
       </c>
       <c r="G22" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.069</v>
+        <v>1.77</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>上家湖北兴山农商银行，下家沧州银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家赣州农商行、陕西陇县农商行，下家汇添富基金、潍坊银行、平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2、 240205 1.7375 2000 +0 宁波通商银行 出给 陕西凤翔农商银行</t>
+          <t>2. 250205 1.77 1E +0 赣州农商行 4K 请求 +陕西陇县农商行6K 请求 出给 汇添富基金5K 请求 + 潍坊银行 2K + 平安银行3K</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1365,33 +1365,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宁波通商银行</t>
+          <t>陕西陇县农商行</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>240205</v>
+        <v>250205</v>
       </c>
       <c r="G23" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7375</v>
+        <v>1.77</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>上家宁波通商银行，下家陕西凤翔农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家赣州农商行、陕西陇县农商行，下家汇添富基金、潍坊银行、平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2、 240205 1.7375 2000 +0 宁波通商银行 出给 陕西凤翔农商银行</t>
+          <t>2. 250205 1.77 1E +0 赣州农商行 4K 请求 +陕西陇县农商行6K 请求 出给 汇添富基金5K 请求 + 潍坊银行 2K + 平安银行3K</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1406,38 +1406,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>陕西凤翔农商银行</t>
+          <t>汇添富基金</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>240205</v>
+        <v>250205</v>
       </c>
       <c r="G24" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7375</v>
+        <v>1.77</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>上家宁波通商银行，下家陕西凤翔农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家赣州农商行、陕西陇县农商行，下家汇添富基金、潍坊银行、平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3、 230210 1.70 2000 +0 新疆银行 出给 陕西石泉农商银行</t>
+          <t>2. 250205 1.77 1E +0 赣州农商行 4K 请求 +陕西陇县农商行6K 请求 出给 汇添富基金5K 请求 + 潍坊银行 2K + 平安银行3K</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1447,33 +1447,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>新疆银行</t>
+          <t>潍坊银行</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>230210</v>
+        <v>250205</v>
       </c>
       <c r="G25" t="n">
         <v>2000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>上家新疆银行，下家陕西石泉农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家赣州农商行、陕西陇县农商行，下家汇添富基金、潍坊银行、平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3、 230210 1.70 2000 +0 新疆银行 出给 陕西石泉农商银行</t>
+          <t>2. 250205 1.77 1E +0 赣州农商行 4K 请求 +陕西陇县农商行6K 请求 出给 汇添富基金5K 请求 + 潍坊银行 2K + 平安银行3K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1488,33 +1488,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>陕西石泉农商银行</t>
+          <t>平安银行</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>230210</v>
+        <v>250205</v>
       </c>
       <c r="G26" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>上家新疆银行，下家陕西石泉农商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家赣州农商行、陕西陇县农商行，下家汇添富基金、潍坊银行、平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1. 240013 1.44 2000 +0 正安县农联社 请求 出给 网商银行</t>
+          <t>3. 260005 1.73 1.3E +0 陕西榆林农商银行1E 请求+ 武功县农信社3K 请求 出给 上海攀赢基金公司 4K +申港证券 5K +常熟农村商行 4K</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1529,38 +1529,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>正安县农联社</t>
+          <t>陕西榆林农商银行</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>240013</v>
+        <v>260005</v>
       </c>
       <c r="G27" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>上家正安县农联社，下家网商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西榆林农商银行、武功县农信社，下家上海攀赢基金公司、申港证券、常熟农村商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1. 240013 1.44 2000 +0 正安县农联社 请求 出给 网商银行</t>
+          <t>3. 260005 1.73 1.3E +0 陕西榆林农商银行1E 请求+ 武功县农信社3K 请求 出给 上海攀赢基金公司 4K +申港证券 5K +常熟农村商行 4K</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1570,38 +1570,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>网商银行</t>
+          <t>武功县农信社</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>240013</v>
+        <v>260005</v>
       </c>
       <c r="G28" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>上家正安县农联社，下家网商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西榆林农商银行、武功县农信社，下家上海攀赢基金公司、申港证券、常熟农村商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2. 260005 1.7415 2E +0 帮发 兴业银行 赵婧文 2E 出给 陕西杨凌农商行 请求5K +陕西榆林农商银行 请求5K +江苏邳州农商行 请求5K +东方财富证券 5K</t>
+          <t>3. 260005 1.73 1.3E +0 陕西榆林农商银行1E 请求+ 武功县农信社3K 请求 出给 上海攀赢基金公司 4K +申港证券 5K +常熟农村商行 4K</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>兴业银行（赵婧文）</t>
+          <t>上海攀赢基金公司</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>260005</v>
       </c>
       <c r="G29" t="n">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7415</v>
+        <v>1.73</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>上家兴业银行，下家陕西杨凌农商行、陕西榆林农商银行、江苏邳州农商行、东方财富证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西榆林农商银行、武功县农信社，下家上海攀赢基金公司、申港证券、常熟农村商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2. 260005 1.7415 2E +0 帮发 兴业银行 赵婧文 2E 出给 陕西杨凌农商行 请求5K +陕西榆林农商银行 请求5K +江苏邳州农商行 请求5K +东方财富证券 5K</t>
+          <t>3. 260005 1.73 1.3E +0 陕西榆林农商银行1E 请求+ 武功县农信社3K 请求 出给 上海攀赢基金公司 4K +申港证券 5K +常熟农村商行 4K</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>陕西杨凌农商行</t>
+          <t>申港证券</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1667,18 +1667,18 @@
         <v>5000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7415</v>
+        <v>1.73</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>上家兴业银行，下家陕西杨凌农商行、陕西榆林农商银行、江苏邳州农商行、东方财富证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西榆林农商银行、武功县农信社，下家上海攀赢基金公司、申港证券、常熟农村商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2. 260005 1.7415 2E +0 帮发 兴业银行 赵婧文 2E 出给 陕西杨凌农商行 请求5K +陕西榆林农商银行 请求5K +江苏邳州农商行 请求5K +东方财富证券 5K</t>
+          <t>3. 260005 1.73 1.3E +0 陕西榆林农商银行1E 请求+ 武功县农信社3K 请求 出给 上海攀赢基金公司 4K +申港证券 5K +常熟农村商行 4K</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1693,38 +1693,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>陕西榆林农商银行</t>
+          <t>常熟农村商行</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>260005</v>
       </c>
       <c r="G31" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7415</v>
+        <v>1.73</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>上家兴业银行，下家陕西杨凌农商行、陕西榆林农商银行、江苏邳州农商行、东方财富证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家陕西榆林农商银行、武功县农信社，下家上海攀赢基金公司、申港证券、常熟农村商行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2. 260005 1.7415 2E +0 帮发 兴业银行 赵婧文 2E 出给 陕西杨凌农商行 请求5K +陕西榆林农商银行 请求5K +江苏邳州农商行 请求5K +东方财富证券 5K</t>
+          <t>4. 260005 1.735 2000 +0 泾阳县农联社 请求 出给 上海攀赢基金公司</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1734,33 +1734,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>江苏邳州农商行</t>
+          <t>泾阳县农联社</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>260005</v>
       </c>
       <c r="G32" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7415</v>
+        <v>1.735</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>上家兴业银行，下家陕西杨凌农商行、陕西榆林农商银行、江苏邳州农商行、东方财富证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家泾阳县农联社，下家上海攀赢基金公司，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2. 260005 1.7415 2E +0 帮发 兴业银行 赵婧文 2E 出给 陕西杨凌农商行 请求5K +陕西榆林农商银行 请求5K +江苏邳州农商行 请求5K +东方财富证券 5K</t>
+          <t>4. 260005 1.735 2000 +0 泾阳县农联社 请求 出给 上海攀赢基金公司</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1775,33 +1775,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>东方财富证券</t>
+          <t>上海攀赢基金公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>260005</v>
       </c>
       <c r="G33" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7415</v>
+        <v>1.735</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>上家兴业银行，下家陕西杨凌农商行、陕西榆林农商银行、江苏邳州农商行、东方财富证券，履行做市商职责，上下家不偏离。</t>
+          <t>上家泾阳县农联社，下家上海攀赢基金公司，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3. 260205 1.8075 4000 +0 广东化州农商银行 请求 出给 潍坊银行</t>
+          <t>5. 260005 1.7375 2000 +0 江苏沛县农商行 请求 出给 祁县农商银行 请求</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1816,33 +1816,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>广东化州农商银行</t>
+          <t>江苏沛县农商行</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>260205</v>
+        <v>260005</v>
       </c>
       <c r="G34" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8075</v>
+        <v>1.7375</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>上家广东化州农商银行，下家潍坊银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家江苏沛县农商行，下家祁县农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3. 260205 1.8075 4000 +0 广东化州农商银行 请求 出给 潍坊银行</t>
+          <t>5. 260005 1.7375 2000 +0 江苏沛县农商行 请求 出给 祁县农商银行 请求</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1857,33 +1857,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>潍坊银行</t>
+          <t>祁县农商银行</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>260205</v>
+        <v>260005</v>
       </c>
       <c r="G35" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8075</v>
+        <v>1.7375</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>上家广东化州农商银行，下家潍坊银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家江苏沛县农商行，下家祁县农商银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4. 250215 1.8155 2000 +0 浙江海盐农商银行 请求 出给 宁波通商银行</t>
+          <t>6. 260010 1.734 2000 +0 上海攀赢基金公司 出给 工银瑞信添利固定收益养老金产品 请求</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1898,33 +1898,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>浙江海盐农商银行</t>
+          <t>上海攀赢基金公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>250215</v>
+        <v>260010</v>
       </c>
       <c r="G36" t="n">
         <v>2000</v>
       </c>
       <c r="H36" t="n">
-        <v>1.8155</v>
+        <v>1.734</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>上家浙江海盐农商银行，下家宁波通商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家上海攀赢基金公司，下家工银瑞信添利固定收益养老金产品，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4. 250215 1.8155 2000 +0 浙江海盐农商银行 请求 出给 宁波通商银行</t>
+          <t>6. 260010 1.734 2000 +0 上海攀赢基金公司 出给 工银瑞信添利固定收益养老金产品 请求</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1939,33 +1939,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宁波通商银行</t>
+          <t>工银瑞信添利固定收益养老金产品</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>250215</v>
+        <v>260010</v>
       </c>
       <c r="G37" t="n">
         <v>2000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8155</v>
+        <v>1.734</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>上家浙江海盐农商银行，下家宁波通商银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家上海攀赢基金公司，下家工银瑞信添利固定收益养老金产品，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5. 260205 1.811 3000 +0 江苏滨海农商银行 请求 出给 申港证券2K+江西裕民银行1K</t>
+          <t>1、 2400004 2.26 3000 +0 平安证券 出给 平安银行</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1980,33 +1980,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>江苏滨海农商银行</t>
+          <t>平安证券</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>260205</v>
+        <v>2400004</v>
       </c>
       <c r="G38" t="n">
         <v>3000</v>
       </c>
       <c r="H38" t="n">
-        <v>1.811</v>
+        <v>2.26</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>上家江苏滨海农商银行，下家申港证券、江西裕民银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家平安证券，下家平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5. 260205 1.811 3000 +0 江苏滨海农商银行 请求 出给 申港证券2K+江西裕民银行1K</t>
+          <t>1、 2400004 2.26 3000 +0 平安证券 出给 平安银行</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2021,38 +2021,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>申港证券</t>
+          <t>平安银行</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>260205</v>
+        <v>2400004</v>
       </c>
       <c r="G39" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H39" t="n">
-        <v>1.811</v>
+        <v>2.26</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>上家江苏滨海农商银行，下家申港证券、江西裕民银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家平安证券，下家平安银行，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5. 260205 1.811 3000 +0 江苏滨海农商银行 请求 出给 申港证券2K+江西裕民银行1K</t>
+          <t>2、 260010 1.734 1000 +0 平安银行 出给 平安证券</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2062,26 +2062,1256 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>江西裕民银行</t>
+          <t>平安银行</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>260205</v>
+        <v>260010</v>
       </c>
       <c r="G40" t="n">
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.811</v>
+        <v>1.734</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>上家江苏滨海农商银行，下家申港证券、江西裕民银行，履行做市商职责，上下家不偏离。</t>
+          <t>上家平安银行，下家平安证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2、 260010 1.734 1000 +0 平安银行 出给 平安证券</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>平安证券</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>260010</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.734</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>上家平安银行，下家平安证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3、 260007 1.576 3000 +0 陕西丹凤农商银行 出给 三原县农信社</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>陕西丹凤农商银行</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>260007</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>上家陕西丹凤农商银行，下家三原县农信社，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3、 260007 1.576 3000 +0 陕西丹凤农商银行 出给 三原县农信社</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>三原县农信社</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>260007</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>上家陕西丹凤农商银行，下家三原县农信社，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4、29.18Y 2505749 25重庆债37 2.29 5000 +0 陕西秦农农商银行 出给 中国人寿资产</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>陕西秦农农商银行</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2505749</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>上家陕西秦农农商银行，下家中国人寿资产，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4、29.18Y 2505749 25重庆债37 2.29 5000 +0 陕西秦农农商银行 出给 中国人寿资产</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>中国人寿资产</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2505749</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>上家陕西秦农农商银行，下家中国人寿资产，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1) 28.91Y 2500002 2.208 2E 05.28+0 内蒙古农商银行2E 出给 广东华兴银行5K+ 平安证券5K+ 上海农商银行5K+ 华福证券5K</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>内蒙古农商银行</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G46" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家广东华兴银行、平安证券、上海农商银行、华福证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1) 28.91Y 2500002 2.208 2E 05.28+0 内蒙古农商银行2E 出给 广东华兴银行5K+ 平安证券5K+ 上海农商银行5K+ 华福证券5K</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>广东华兴银行</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家广东华兴银行、平安证券、上海农商银行、华福证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1) 28.91Y 2500002 2.208 2E 05.28+0 内蒙古农商银行2E 出给 广东华兴银行5K+ 平安证券5K+ 上海农商银行5K+ 华福证券5K</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>平安证券</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家广东华兴银行、平安证券、上海农商银行、华福证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1) 28.91Y 2500002 2.208 2E 05.28+0 内蒙古农商银行2E 出给 广东华兴银行5K+ 平安证券5K+ 上海农商银行5K+ 华福证券5K</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>上海农商银行</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家广东华兴银行、平安证券、上海农商银行、华福证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1) 28.91Y 2500002 2.208 2E 05.28+0 内蒙古农商银行2E 出给 广东华兴银行5K+ 平安证券5K+ 上海农商银行5K+ 华福证券5K</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>华福证券</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2.208</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家广东华兴银行、平安证券、上海农商银行、华福证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2) 28.91Y 2500002 2.21 3E 05.28+0 内蒙古农商银行3E 出给 成都银行1.7E+ 申港证券3K+ 潍坊银行5K+ 财信证券5K</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>内蒙古农商银行</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G51" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家成都银行、申港证券、潍坊银行、财信证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2) 28.91Y 2500002 2.21 3E 05.28+0 内蒙古农商银行3E 出给 成都银行1.7E+ 申港证券3K+ 潍坊银行5K+ 财信证券5K</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>成都银行</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家成都银行、申港证券、潍坊银行、财信证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2) 28.91Y 2500002 2.21 3E 05.28+0 内蒙古农商银行3E 出给 成都银行1.7E+ 申港证券3K+ 潍坊银行5K+ 财信证券5K</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>申港证券</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家成都银行、申港证券、潍坊银行、财信证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2) 28.91Y 2500002 2.21 3E 05.28+0 内蒙古农商银行3E 出给 成都银行1.7E+ 申港证券3K+ 潍坊银行5K+ 财信证券5K</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>潍坊银行</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家成都银行、申港证券、潍坊银行、财信证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2) 28.91Y 2500002 2.21 3E 05.28+0 内蒙古农商银行3E 出给 成都银行1.7E+ 申港证券3K+ 潍坊银行5K+ 财信证券5K</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>财信证券</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2500002</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>上家内蒙古农商银行，下家成都银行、申港证券、潍坊银行、财信证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3) 9.28Y 250220 1.799 3000 05.28+0 辽宁农商银行3K 出给 江海证券2K+ 兴业证券1K</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>辽宁农商银行</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>250220</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>上家辽宁农商银行，下家江海证券、兴业证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3) 9.28Y 250220 1.799 3000 05.28+0 辽宁农商银行3K 出给 江海证券2K+ 兴业证券1K</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>江海证券</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>250220</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>上家辽宁农商银行，下家江海证券、兴业证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3) 9.28Y 250220 1.799 3000 05.28+0 辽宁农商银行3K 出给 江海证券2K+ 兴业证券1K</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>兴业证券</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>250220</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>上家辽宁农商银行，下家江海证券、兴业证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4) 9.78Y 260205 1.785 2000 05.28+0 夏津农商银行 出给 江苏建湖农商行</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>夏津农商银行</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>上家夏津农商银行，下家江苏建湖农商行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4) 9.78Y 260205 1.785 2000 05.28+0 夏津农商银行 出给 江苏建湖农商行</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>江苏建湖农商行</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>上家夏津农商银行，下家江苏建湖农商行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5) 9.78Y 260205 1.803 2000 05.28+0 常熟农村商行 出给 陕西杨凌农商行</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>常熟农村商行</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>上家常熟农村商行，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5) 9.78Y 260205 1.803 2000 05.28+0 常熟农村商行 出给 陕西杨凌农商行</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>陕西杨凌农商行</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>上家常熟农村商行，下家陕西杨凌农商行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6) 29.25Y 2500006 2.2525 2000 05.28+0 浙江丽水莲都农商行 出给 重庆三峡银行</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>浙江丽水莲都农商行</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2500006</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.2525</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>上家浙江丽水莲都农商行，下家重庆三峡银行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6) 29.25Y 2500006 2.2525 2000 05.28+0 浙江丽水莲都农商行 出给 重庆三峡银行</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>重庆三峡银行</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2500006</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2.2525</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>上家浙江丽水莲都农商行，下家重庆三峡银行，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1） 260205 1.802 5000 +0 宝鸡渭滨农商银行 出给 勉县农联社</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>宝鸡渭滨农商银行</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>上家宝鸡渭滨农商银行，下家勉县农联社，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1） 260205 1.802 5000 +0 宝鸡渭滨农商银行 出给 勉县农联社</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>勉县农联社</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>上家宝鸡渭滨农商银行，下家勉县农联社，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2） 260205 1.7925 5000 +0 江门农商银行 出给 方正证券</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>江门农商银行</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.7925</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>上家江门农商银行，下家方正证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2） 260205 1.7925 5000 +0 江门农商银行 出给 方正证券</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>方正证券</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>260205</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.7925</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>上家江门农商银行，下家方正证券，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3） 230022 1.235 9000 +0 青海循化农商银行（请求，青海循化农商银行) 出给 东亚银行上海（对话)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>青海循化农商银行</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>230022</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>上家青海循化农商银行，下家东亚银行上海，履行做市商职责，上下家不偏离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3） 230022 1.235 9000 +0 青海循化农商银行（请求，青海循化农商银行) 出给 东亚银行上海（对话)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>T+0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>东亚银行上海</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>230022</v>
+      </c>
+      <c r="G70" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>上家青海循化农商银行，下家东亚银行上海，履行做市商职责，上下家不偏离。</t>
         </is>
       </c>
     </row>
